--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K585"/>
+  <dimension ref="A1:K587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23245,6 +23245,84 @@
       <c r="K585" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>358.73</v>
+      </c>
+      <c r="C586" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="D586" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="E586" t="n">
+        <v>367.95</v>
+      </c>
+      <c r="F586" t="n">
+        <v>362.89</v>
+      </c>
+      <c r="G586" t="n">
+        <v>346.43</v>
+      </c>
+      <c r="H586" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="I586" t="n">
+        <v>359.81</v>
+      </c>
+      <c r="J586" t="n">
+        <v>366.52</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>357.98</v>
+      </c>
+      <c r="C587" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="D587" t="n">
+        <v>367.19</v>
+      </c>
+      <c r="E587" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="F587" t="n">
+        <v>363.03</v>
+      </c>
+      <c r="G587" t="n">
+        <v>345.89</v>
+      </c>
+      <c r="H587" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="I587" t="n">
+        <v>358.87</v>
+      </c>
+      <c r="J587" t="n">
+        <v>366.7</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23259,7 +23337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B688"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30142,6 +30220,36 @@
       </c>
       <c r="B688" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>-0.29</v>
       </c>
     </row>
   </sheetData>
@@ -30310,28 +30418,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1601036800974557</v>
+        <v>-0.1576696355112191</v>
       </c>
       <c r="J2" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K2" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06541380063440883</v>
+        <v>0.0638969022476028</v>
       </c>
       <c r="M2" t="n">
-        <v>3.206206299656294</v>
+        <v>3.20569577692231</v>
       </c>
       <c r="N2" t="n">
-        <v>16.23733274225235</v>
+        <v>16.21627068128338</v>
       </c>
       <c r="O2" t="n">
-        <v>4.029557387884227</v>
+        <v>4.026943093871997</v>
       </c>
       <c r="P2" t="n">
-        <v>359.3912254187386</v>
+        <v>359.3623197682491</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30392,28 +30500,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.866064492098422</v>
+        <v>-6.835854784424879</v>
       </c>
       <c r="J3" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K3" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4951618305359847</v>
+        <v>0.4942902355158139</v>
       </c>
       <c r="M3" t="n">
-        <v>34.94862974779481</v>
+        <v>34.93032093644519</v>
       </c>
       <c r="N3" t="n">
-        <v>2079.275577657777</v>
+        <v>2077.195152972318</v>
       </c>
       <c r="O3" t="n">
-        <v>45.59907430702707</v>
+        <v>45.57625646070899</v>
       </c>
       <c r="P3" t="n">
-        <v>498.0114827043562</v>
+        <v>497.6480107296143</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30474,28 +30582,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04467538246668312</v>
+        <v>0.04587035275439016</v>
       </c>
       <c r="J4" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K4" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006114045145254265</v>
+        <v>0.006489007883069942</v>
       </c>
       <c r="M4" t="n">
-        <v>2.873973323933214</v>
+        <v>2.870062364097838</v>
       </c>
       <c r="N4" t="n">
-        <v>14.32664911178552</v>
+        <v>14.28637925775391</v>
       </c>
       <c r="O4" t="n">
-        <v>3.785056024920307</v>
+        <v>3.7797326966009</v>
       </c>
       <c r="P4" t="n">
-        <v>364.8125734061267</v>
+        <v>364.7983728322786</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30556,28 +30664,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04188742411934357</v>
+        <v>-0.04113509949422522</v>
       </c>
       <c r="J5" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K5" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007667075759820507</v>
+        <v>0.007450486551956681</v>
       </c>
       <c r="M5" t="n">
-        <v>2.492709083073933</v>
+        <v>2.487196819761018</v>
       </c>
       <c r="N5" t="n">
-        <v>10.02755627970061</v>
+        <v>9.996691507380737</v>
       </c>
       <c r="O5" t="n">
-        <v>3.166631693092932</v>
+        <v>3.161754498277932</v>
       </c>
       <c r="P5" t="n">
-        <v>367.8842171857464</v>
+        <v>367.875276523188</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30634,28 +30742,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09079011198372787</v>
+        <v>-0.08992331586560592</v>
       </c>
       <c r="J6" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K6" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02193782744938111</v>
+        <v>0.02168725678160677</v>
       </c>
       <c r="M6" t="n">
-        <v>3.158587247025731</v>
+        <v>3.152021285214559</v>
       </c>
       <c r="N6" t="n">
-        <v>16.22744341657303</v>
+        <v>16.17638054546723</v>
       </c>
       <c r="O6" t="n">
-        <v>4.028330102731531</v>
+        <v>4.021987138898784</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2224283641218</v>
+        <v>364.2121252164862</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30712,28 +30820,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1361246364189669</v>
+        <v>-0.1360226371188007</v>
       </c>
       <c r="J7" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K7" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0832937881001915</v>
+        <v>0.08376662742625351</v>
       </c>
       <c r="M7" t="n">
-        <v>2.411815684401375</v>
+        <v>2.40441707601041</v>
       </c>
       <c r="N7" t="n">
-        <v>9.005154737844862</v>
+        <v>8.974723907893994</v>
       </c>
       <c r="O7" t="n">
-        <v>3.000858999993979</v>
+        <v>2.995784356039999</v>
       </c>
       <c r="P7" t="n">
-        <v>349.6073087062495</v>
+        <v>349.606098358108</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -30794,28 +30902,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2261285932716598</v>
+        <v>-0.2254259131459851</v>
       </c>
       <c r="J8" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K8" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1665924670450468</v>
+        <v>0.1667626194974503</v>
       </c>
       <c r="M8" t="n">
-        <v>2.371121230949028</v>
+        <v>2.365836979808682</v>
       </c>
       <c r="N8" t="n">
-        <v>11.29570073267989</v>
+        <v>11.26007678566797</v>
       </c>
       <c r="O8" t="n">
-        <v>3.360907724511325</v>
+        <v>3.355603788540591</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0354461812344</v>
+        <v>355.0270954811874</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30872,28 +30980,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1414133702915131</v>
+        <v>-0.1402422539979923</v>
       </c>
       <c r="J9" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K9" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06187700139518537</v>
+        <v>0.06132388825189095</v>
       </c>
       <c r="M9" t="n">
-        <v>2.612349933616257</v>
+        <v>2.608013307925558</v>
       </c>
       <c r="N9" t="n">
-        <v>13.38787421172315</v>
+        <v>13.35080611359758</v>
       </c>
       <c r="O9" t="n">
-        <v>3.658944412220983</v>
+        <v>3.653875492350223</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5336120601593</v>
+        <v>361.5196958574162</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -30950,28 +31058,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.101892379050051</v>
+        <v>-0.1008703567201754</v>
       </c>
       <c r="J10" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K10" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04748646850133864</v>
+        <v>0.0468970741197996</v>
       </c>
       <c r="M10" t="n">
-        <v>2.445303389196355</v>
+        <v>2.441816490253126</v>
       </c>
       <c r="N10" t="n">
-        <v>9.195700961726041</v>
+        <v>9.170326706746957</v>
       </c>
       <c r="O10" t="n">
-        <v>3.032441419339546</v>
+        <v>3.028254729501294</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9585375832853</v>
+        <v>367.9463892993632</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31009,7 +31117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K585"/>
+  <dimension ref="A1:K587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64325,6 +64433,120 @@
         </is>
       </c>
     </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-45.36228290102306,170.86242330178348</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-45.3629188191651,170.86247527406013</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-45.36351165393986,170.8625362093972</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-45.364054740632156,170.8627967752755</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-45.364648282162086,170.8630545253717</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-45.36528560525461,170.8632083587042</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>-45.365880619505845,170.86345742486074</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>-45.3663620636758,170.86393538645345</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>-45.366663731250014,170.8646357388879</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-45.36228342701372,170.8624137577439</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-45.36291876840386,170.86247170076555</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-45.36351221527169,170.86252718165795</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-45.36405579019346,170.86279229318757</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-45.36464783186043,170.863056194368</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-45.36528703100009,170.86320176906938</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-45.36588163266073,170.86345319459832</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>-45.366367247772814,170.86392590510408</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>-45.36666247854923,170.86463719540322</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K587"/>
+  <dimension ref="A1:K588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23323,6 +23323,45 @@
       <c r="K587" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="C588" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="D588" t="n">
+        <v>365.36</v>
+      </c>
+      <c r="E588" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="F588" t="n">
+        <v>361.55</v>
+      </c>
+      <c r="G588" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="H588" t="n">
+        <v>348.35</v>
+      </c>
+      <c r="I588" t="n">
+        <v>356.79</v>
+      </c>
+      <c r="J588" t="n">
+        <v>365.92</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -23337,7 +23376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30250,6 +30289,16 @@
       </c>
       <c r="B691" t="n">
         <v>-0.29</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -30418,28 +30467,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1576696355112191</v>
+        <v>-0.1571020174708603</v>
       </c>
       <c r="J2" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K2" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0638969022476028</v>
+        <v>0.06368251944057113</v>
       </c>
       <c r="M2" t="n">
-        <v>3.20569577692231</v>
+        <v>3.202647380954312</v>
       </c>
       <c r="N2" t="n">
-        <v>16.21627068128338</v>
+        <v>16.19222684819722</v>
       </c>
       <c r="O2" t="n">
-        <v>4.026943093871997</v>
+        <v>4.023956616092825</v>
       </c>
       <c r="P2" t="n">
-        <v>359.3623197682491</v>
+        <v>359.355562381653</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30500,28 +30549,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.835854784424879</v>
+        <v>-6.820828492277748</v>
       </c>
       <c r="J3" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K3" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4942902355158139</v>
+        <v>0.4938606903586927</v>
       </c>
       <c r="M3" t="n">
-        <v>34.93032093644519</v>
+        <v>34.9205241100503</v>
       </c>
       <c r="N3" t="n">
-        <v>2077.195152972318</v>
+        <v>2076.144387069633</v>
       </c>
       <c r="O3" t="n">
-        <v>45.57625646070899</v>
+        <v>45.56472744425925</v>
       </c>
       <c r="P3" t="n">
-        <v>497.6480107296143</v>
+        <v>497.4668009092877</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30582,28 +30631,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04587035275439016</v>
+        <v>0.04562154645650543</v>
       </c>
       <c r="J4" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K4" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006489007883069942</v>
+        <v>0.006443610412822265</v>
       </c>
       <c r="M4" t="n">
-        <v>2.870062364097838</v>
+        <v>2.866150103174689</v>
       </c>
       <c r="N4" t="n">
-        <v>14.28637925775391</v>
+        <v>14.26275243742798</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7797326966009</v>
+        <v>3.776605941507266</v>
       </c>
       <c r="P4" t="n">
-        <v>364.7983728322786</v>
+        <v>364.8013370524743</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30664,28 +30713,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04113509949422522</v>
+        <v>-0.04109483914323325</v>
       </c>
       <c r="J5" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K5" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007450486551956681</v>
+        <v>0.007464557555766471</v>
       </c>
       <c r="M5" t="n">
-        <v>2.487196819761018</v>
+        <v>2.483118563706365</v>
       </c>
       <c r="N5" t="n">
-        <v>9.996691507380737</v>
+        <v>9.979679988707211</v>
       </c>
       <c r="O5" t="n">
-        <v>3.161754498277932</v>
+        <v>3.159063150477877</v>
       </c>
       <c r="P5" t="n">
-        <v>367.875276523188</v>
+        <v>367.8747968707576</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30742,28 +30791,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08992331586560592</v>
+        <v>-0.09003541796347539</v>
       </c>
       <c r="J6" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K6" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02168725678160677</v>
+        <v>0.02182226787502817</v>
       </c>
       <c r="M6" t="n">
-        <v>3.152021285214559</v>
+        <v>3.147099926785289</v>
       </c>
       <c r="N6" t="n">
-        <v>16.17638054546723</v>
+        <v>16.14896719045068</v>
       </c>
       <c r="O6" t="n">
-        <v>4.021987138898784</v>
+        <v>4.018577757173635</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2121252164862</v>
+        <v>364.2134607747309</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30820,28 +30869,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1360226371188007</v>
+        <v>-0.1366054322109131</v>
       </c>
       <c r="J7" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K7" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08376662742625351</v>
+        <v>0.08469042910470825</v>
       </c>
       <c r="M7" t="n">
-        <v>2.40441707601041</v>
+        <v>2.403336793325942</v>
       </c>
       <c r="N7" t="n">
-        <v>8.974723907893994</v>
+        <v>8.963336530020188</v>
       </c>
       <c r="O7" t="n">
-        <v>2.995784356039999</v>
+        <v>2.993883185767305</v>
       </c>
       <c r="P7" t="n">
-        <v>349.606098358108</v>
+        <v>349.6130416428907</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -30902,28 +30951,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2254259131459851</v>
+        <v>-0.2257088029578914</v>
       </c>
       <c r="J8" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K8" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1667626194974503</v>
+        <v>0.1676381537820505</v>
       </c>
       <c r="M8" t="n">
-        <v>2.365836979808682</v>
+        <v>2.363182397631822</v>
       </c>
       <c r="N8" t="n">
-        <v>11.26007678566797</v>
+        <v>11.24181368503893</v>
       </c>
       <c r="O8" t="n">
-        <v>3.355603788540591</v>
+        <v>3.352881400383696</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0270954811874</v>
+        <v>355.0304657644186</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -30980,28 +31029,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1402422539979923</v>
+        <v>-0.1406398683948144</v>
       </c>
       <c r="J9" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K9" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06132388825189095</v>
+        <v>0.06186648847028375</v>
       </c>
       <c r="M9" t="n">
-        <v>2.608013307925558</v>
+        <v>2.605538318896134</v>
       </c>
       <c r="N9" t="n">
-        <v>13.35080611359758</v>
+        <v>13.32987813580594</v>
       </c>
       <c r="O9" t="n">
-        <v>3.653875492350223</v>
+        <v>3.651010563639324</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5196958574162</v>
+        <v>361.5244329425911</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31058,28 +31107,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1008703567201754</v>
+        <v>-0.100626773021493</v>
       </c>
       <c r="J10" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="K10" t="n">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0468970741197996</v>
+        <v>0.04685022462607391</v>
       </c>
       <c r="M10" t="n">
-        <v>2.441816490253126</v>
+        <v>2.438805760999356</v>
       </c>
       <c r="N10" t="n">
-        <v>9.170326706746957</v>
+        <v>9.155385937534939</v>
       </c>
       <c r="O10" t="n">
-        <v>3.028254729501294</v>
+        <v>3.025786829493271</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9463892993632</v>
+        <v>367.9434872999962</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31117,7 +31166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K587"/>
+  <dimension ref="A1:K588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64547,6 +64596,63 @@
         </is>
       </c>
     </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-45.36228433872899,170.86239721474158</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-45.36291875208773,170.86247055220662</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-45.36351366208141,170.86250391297725</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-45.36405771911647,170.86278405583633</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-45.36465259219108,170.86303855069158</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-45.3652907009728,170.86318480685986</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>-45.36588591685683,170.86343530662975</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>-45.36637871896323,170.8639049250909</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>-45.366667906919155,170.8646308838363</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K588"/>
+  <dimension ref="A1:K590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23360,6 +23360,84 @@
         <v>365.92</v>
       </c>
       <c r="K588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="C589" t="n">
+        <v>371.27</v>
+      </c>
+      <c r="D589" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="E589" t="n">
+        <v>367.98</v>
+      </c>
+      <c r="F589" t="n">
+        <v>362.69</v>
+      </c>
+      <c r="G589" t="n">
+        <v>345.34</v>
+      </c>
+      <c r="H589" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="I589" t="n">
+        <v>357.61</v>
+      </c>
+      <c r="J589" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>356.3</v>
+      </c>
+      <c r="C590" t="n">
+        <v>384.46</v>
+      </c>
+      <c r="D590" t="n">
+        <v>370.34</v>
+      </c>
+      <c r="E590" t="n">
+        <v>368.87</v>
+      </c>
+      <c r="F590" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="G590" t="n">
+        <v>344.71</v>
+      </c>
+      <c r="H590" t="n">
+        <v>350.35</v>
+      </c>
+      <c r="I590" t="n">
+        <v>358.88</v>
+      </c>
+      <c r="J590" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="K590" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -23376,7 +23454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B692"/>
+  <dimension ref="A1:B694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30299,6 +30377,26 @@
       </c>
       <c r="B692" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -30467,28 +30565,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1571020174708603</v>
+        <v>-0.156263864783053</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K2" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06368251944057113</v>
+        <v>0.06349140624482863</v>
       </c>
       <c r="M2" t="n">
-        <v>3.202647380954312</v>
+        <v>3.195279745315946</v>
       </c>
       <c r="N2" t="n">
-        <v>16.19222684819722</v>
+        <v>16.14101492693085</v>
       </c>
       <c r="O2" t="n">
-        <v>4.023956616092825</v>
+        <v>4.017588197778718</v>
       </c>
       <c r="P2" t="n">
-        <v>359.355562381653</v>
+        <v>359.345555885699</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30549,28 +30647,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.820828492277748</v>
+        <v>-6.773419856412995</v>
       </c>
       <c r="J3" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K3" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4938606903586927</v>
+        <v>0.4908058913352424</v>
       </c>
       <c r="M3" t="n">
-        <v>34.9205241100503</v>
+        <v>34.95838052042419</v>
       </c>
       <c r="N3" t="n">
-        <v>2076.144387069633</v>
+        <v>2081.693074832155</v>
       </c>
       <c r="O3" t="n">
-        <v>45.56472744425925</v>
+        <v>45.62557478906052</v>
       </c>
       <c r="P3" t="n">
-        <v>497.4668009092877</v>
+        <v>496.8934543812527</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30631,28 +30729,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04562154645650543</v>
+        <v>0.04740835230149078</v>
       </c>
       <c r="J4" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K4" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006443610412822265</v>
+        <v>0.006992838117014344</v>
       </c>
       <c r="M4" t="n">
-        <v>2.866150103174689</v>
+        <v>2.865164655858704</v>
       </c>
       <c r="N4" t="n">
-        <v>14.26275243742798</v>
+        <v>14.24623016918397</v>
       </c>
       <c r="O4" t="n">
-        <v>3.776605941507266</v>
+        <v>3.774417858317222</v>
       </c>
       <c r="P4" t="n">
-        <v>364.8013370524743</v>
+        <v>364.7799818639704</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30713,28 +30811,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04109483914323325</v>
+        <v>-0.03984118151450872</v>
       </c>
       <c r="J5" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K5" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007464557555766471</v>
+        <v>0.007066660365926625</v>
       </c>
       <c r="M5" t="n">
-        <v>2.483118563706365</v>
+        <v>2.479575629039554</v>
       </c>
       <c r="N5" t="n">
-        <v>9.979679988707211</v>
+        <v>9.955466611261414</v>
       </c>
       <c r="O5" t="n">
-        <v>3.159063150477877</v>
+        <v>3.155228456270863</v>
       </c>
       <c r="P5" t="n">
-        <v>367.8747968707576</v>
+        <v>367.8598172134868</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30791,28 +30889,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09003541796347539</v>
+        <v>-0.08935971520261586</v>
       </c>
       <c r="J6" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K6" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02182226787502817</v>
+        <v>0.02166331718652192</v>
       </c>
       <c r="M6" t="n">
-        <v>3.147099926785289</v>
+        <v>3.139669859373479</v>
       </c>
       <c r="N6" t="n">
-        <v>16.14896719045068</v>
+        <v>16.09675220968274</v>
       </c>
       <c r="O6" t="n">
-        <v>4.018577757173635</v>
+        <v>4.012075798097881</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2134607747309</v>
+        <v>364.2053877375276</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30869,28 +30967,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1366054322109131</v>
+        <v>-0.1373518321590914</v>
       </c>
       <c r="J7" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K7" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08469042910470825</v>
+        <v>0.08611662244060048</v>
       </c>
       <c r="M7" t="n">
-        <v>2.403336793325942</v>
+        <v>2.398996532073895</v>
       </c>
       <c r="N7" t="n">
-        <v>8.963336530020188</v>
+        <v>8.936429454706687</v>
       </c>
       <c r="O7" t="n">
-        <v>2.993883185767305</v>
+        <v>2.989386133423832</v>
       </c>
       <c r="P7" t="n">
-        <v>349.6130416428907</v>
+        <v>349.6219603866073</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -30951,28 +31049,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2257088029578914</v>
+        <v>-0.2249724097116211</v>
       </c>
       <c r="J8" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K8" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1676381537820505</v>
+        <v>0.1677652575058212</v>
       </c>
       <c r="M8" t="n">
-        <v>2.363182397631822</v>
+        <v>2.358073670676087</v>
       </c>
       <c r="N8" t="n">
-        <v>11.24181368503893</v>
+        <v>11.20711070339146</v>
       </c>
       <c r="O8" t="n">
-        <v>3.352881400383696</v>
+        <v>3.347702302085933</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0304657644186</v>
+        <v>355.0216665312818</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31029,28 +31127,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1406398683948144</v>
+        <v>-0.1403012300758171</v>
       </c>
       <c r="J9" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K9" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06186648847028375</v>
+        <v>0.06202809585000946</v>
       </c>
       <c r="M9" t="n">
-        <v>2.605538318896134</v>
+        <v>2.598686360074914</v>
       </c>
       <c r="N9" t="n">
-        <v>13.32987813580594</v>
+        <v>13.28665521534656</v>
       </c>
       <c r="O9" t="n">
-        <v>3.651010563639324</v>
+        <v>3.645086448267937</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5244329425911</v>
+        <v>361.520384716708</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31107,28 +31205,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.100626773021493</v>
+        <v>-0.09892056674265672</v>
       </c>
       <c r="J10" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K10" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04685022462607391</v>
+        <v>0.04560367594433556</v>
       </c>
       <c r="M10" t="n">
-        <v>2.438805760999356</v>
+        <v>2.438700693225764</v>
       </c>
       <c r="N10" t="n">
-        <v>9.155385937534939</v>
+        <v>9.140994050501318</v>
       </c>
       <c r="O10" t="n">
-        <v>3.025786829493271</v>
+        <v>3.023407688437224</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9434872999962</v>
+        <v>367.9231023002749</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31166,7 +31264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K588"/>
+  <dimension ref="A1:K590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64653,6 +64751,120 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-45.36228460522993,170.8623923790947</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-45.36292155829361,170.86266810436413</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-45.363512887287726,170.8625163738009</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-45.36405465553258,170.86279713868802</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-45.36464892545015,170.86305214109126</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-45.36528848314787,170.863195057404</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>-45.365882008975376,170.86345162335792</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>-45.36637419666749,170.86391319605866</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>-45.36665718936792,170.86464334513397</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:25+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-45.36228460522993,170.8623923790947</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-45.36292394910005,170.8628364320999</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-45.36350972485036,170.8625672343027</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-45.364052130911375,170.86280791992593</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-45.36464876462814,170.86305273716138</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-45.365290146516664,170.86318736949596</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-45.36588012740198,170.8634594795596</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>-45.36636719262284,170.86392600596952</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>-45.36665649342299,170.86464415430896</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K590"/>
+  <dimension ref="A1:K592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23368,78 +23368,156 @@
     <row r="589">
       <c r="A589" s="1" t="inlineStr">
         <is>
-          <t>2026-01-31 22:20:38+00:00</t>
+          <t>2026-02-08 22:20:25+00:00</t>
         </is>
       </c>
       <c r="B589" t="n">
         <v>356.3</v>
       </c>
       <c r="C589" t="n">
-        <v>371.27</v>
+        <v>356.96</v>
       </c>
       <c r="D589" t="n">
         <v>366.34</v>
       </c>
       <c r="E589" t="n">
-        <v>367.98</v>
+        <v>368.87</v>
       </c>
       <c r="F589" t="n">
-        <v>362.69</v>
+        <v>362.74</v>
       </c>
       <c r="G589" t="n">
-        <v>345.34</v>
+        <v>344.71</v>
       </c>
       <c r="H589" t="n">
-        <v>349.7</v>
+        <v>350.35</v>
       </c>
       <c r="I589" t="n">
-        <v>357.61</v>
+        <v>358.88</v>
       </c>
       <c r="J589" t="n">
-        <v>367.46</v>
+        <v>367.56</v>
       </c>
       <c r="K589" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
         <is>
-          <t>2026-02-08 22:20:25+00:00</t>
+          <t>2026-03-05 22:14:07+00:00</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>356.3</v>
+        <v>353.38</v>
       </c>
       <c r="C590" t="n">
-        <v>384.46</v>
+        <v>355.2</v>
       </c>
       <c r="D590" t="n">
-        <v>370.34</v>
+        <v>364.17</v>
       </c>
       <c r="E590" t="n">
-        <v>368.87</v>
+        <v>367.16</v>
       </c>
       <c r="F590" t="n">
-        <v>362.74</v>
+        <v>363.15</v>
       </c>
       <c r="G590" t="n">
-        <v>344.71</v>
+        <v>342.72</v>
       </c>
       <c r="H590" t="n">
+        <v>349.04</v>
+      </c>
+      <c r="I590" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="J590" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="C591" t="n">
+        <v>352.68</v>
+      </c>
+      <c r="D591" t="n">
+        <v>360.64</v>
+      </c>
+      <c r="E591" t="n">
+        <v>365.49</v>
+      </c>
+      <c r="F591" t="n">
+        <v>361.26</v>
+      </c>
+      <c r="G591" t="n">
+        <v>342.41</v>
+      </c>
+      <c r="H591" t="n">
+        <v>347.53</v>
+      </c>
+      <c r="I591" t="n">
+        <v>354.67</v>
+      </c>
+      <c r="J591" t="n">
+        <v>364.88</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
         <v>350.35</v>
       </c>
-      <c r="I590" t="n">
-        <v>358.88</v>
-      </c>
-      <c r="J590" t="n">
-        <v>367.56</v>
-      </c>
-      <c r="K590" t="inlineStr">
-        <is>
-          <t>L8</t>
+      <c r="C592" t="n">
+        <v>352.94</v>
+      </c>
+      <c r="D592" t="n">
+        <v>359.91</v>
+      </c>
+      <c r="E592" t="n">
+        <v>364.35</v>
+      </c>
+      <c r="F592" t="n">
+        <v>360.26</v>
+      </c>
+      <c r="G592" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="H592" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="I592" t="n">
+        <v>352.16</v>
+      </c>
+      <c r="J592" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B694"/>
+  <dimension ref="A1:B698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30397,6 +30475,46 @@
       </c>
       <c r="B694" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -30565,28 +30683,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.156263864783053</v>
+        <v>-0.1603169696694472</v>
       </c>
       <c r="J2" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K2" t="n">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06349140624482863</v>
+        <v>0.06687711588501732</v>
       </c>
       <c r="M2" t="n">
-        <v>3.195279745315946</v>
+        <v>3.199316860016856</v>
       </c>
       <c r="N2" t="n">
-        <v>16.14101492693085</v>
+        <v>16.14260443829786</v>
       </c>
       <c r="O2" t="n">
-        <v>4.017588197778718</v>
+        <v>4.017786012009333</v>
       </c>
       <c r="P2" t="n">
-        <v>359.345555885699</v>
+        <v>359.3941127999129</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30647,28 +30765,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.773419856412995</v>
+        <v>-6.761947386619969</v>
       </c>
       <c r="J3" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K3" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4908058913352424</v>
+        <v>0.4923112056767457</v>
       </c>
       <c r="M3" t="n">
-        <v>34.95838052042419</v>
+        <v>34.87515615854517</v>
       </c>
       <c r="N3" t="n">
-        <v>2081.693074832155</v>
+        <v>2071.565979186759</v>
       </c>
       <c r="O3" t="n">
-        <v>45.62557478906052</v>
+        <v>45.51445901234858</v>
       </c>
       <c r="P3" t="n">
-        <v>496.8934543812527</v>
+        <v>496.7527925208965</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30729,28 +30847,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04740835230149078</v>
+        <v>0.0406559076666504</v>
       </c>
       <c r="J4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K4" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006992838117014344</v>
+        <v>0.005162296546497913</v>
       </c>
       <c r="M4" t="n">
-        <v>2.865164655858704</v>
+        <v>2.867294818466535</v>
       </c>
       <c r="N4" t="n">
-        <v>14.24623016918397</v>
+        <v>14.28232167044102</v>
       </c>
       <c r="O4" t="n">
-        <v>3.774417858317222</v>
+        <v>3.7791959026281</v>
       </c>
       <c r="P4" t="n">
-        <v>364.7799818639704</v>
+        <v>364.8608998525371</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30811,28 +30929,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03984118151450872</v>
+        <v>-0.04158908521962487</v>
       </c>
       <c r="J5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K5" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007066660365926625</v>
+        <v>0.0077475595654245</v>
       </c>
       <c r="M5" t="n">
-        <v>2.479575629039554</v>
+        <v>2.476995145919434</v>
       </c>
       <c r="N5" t="n">
-        <v>9.955466611261414</v>
+        <v>9.932491166558931</v>
       </c>
       <c r="O5" t="n">
-        <v>3.155228456270863</v>
+        <v>3.151585500436079</v>
       </c>
       <c r="P5" t="n">
-        <v>367.8598172134868</v>
+        <v>367.8807641339326</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30889,28 +31007,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08935971520261586</v>
+        <v>-0.09000085940175238</v>
       </c>
       <c r="J6" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K6" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02166331718652192</v>
+        <v>0.02212972118650491</v>
       </c>
       <c r="M6" t="n">
-        <v>3.139669859373479</v>
+        <v>3.133211069598623</v>
       </c>
       <c r="N6" t="n">
-        <v>16.09675220968274</v>
+        <v>16.04873541054891</v>
       </c>
       <c r="O6" t="n">
-        <v>4.012075798097881</v>
+        <v>4.006087294424437</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2053877375276</v>
+        <v>364.2130700014486</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30967,28 +31085,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1373518321590914</v>
+        <v>-0.1413921268547371</v>
       </c>
       <c r="J7" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K7" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08611662244060048</v>
+        <v>0.09079257354535886</v>
       </c>
       <c r="M7" t="n">
-        <v>2.398996532073895</v>
+        <v>2.411424485314017</v>
       </c>
       <c r="N7" t="n">
-        <v>8.936429454706687</v>
+        <v>8.97646418483335</v>
       </c>
       <c r="O7" t="n">
-        <v>2.989386133423832</v>
+        <v>2.996074796268169</v>
       </c>
       <c r="P7" t="n">
-        <v>349.6219603866073</v>
+        <v>349.6704235190339</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31049,28 +31167,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2249724097116211</v>
+        <v>-0.2266252903754431</v>
       </c>
       <c r="J8" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K8" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1677652575058212</v>
+        <v>0.1707937008400225</v>
       </c>
       <c r="M8" t="n">
-        <v>2.358073670676087</v>
+        <v>2.355951298134685</v>
       </c>
       <c r="N8" t="n">
-        <v>11.20711070339146</v>
+        <v>11.18020303573767</v>
       </c>
       <c r="O8" t="n">
-        <v>3.347702302085933</v>
+        <v>3.343681060708043</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0216665312818</v>
+        <v>355.0414820830692</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31127,28 +31245,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1403012300758171</v>
+        <v>-0.1439169774793705</v>
       </c>
       <c r="J9" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K9" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06202809585000946</v>
+        <v>0.06521124249016474</v>
       </c>
       <c r="M9" t="n">
-        <v>2.598686360074914</v>
+        <v>2.607570477867351</v>
       </c>
       <c r="N9" t="n">
-        <v>13.28665521534656</v>
+        <v>13.31242776953138</v>
       </c>
       <c r="O9" t="n">
-        <v>3.645086448267937</v>
+        <v>3.648619981517859</v>
       </c>
       <c r="P9" t="n">
-        <v>361.520384716708</v>
+        <v>361.5637612369828</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31205,28 +31323,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09892056674265672</v>
+        <v>-0.09956395449253129</v>
       </c>
       <c r="J10" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="K10" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04560367594433556</v>
+        <v>0.04651725469207257</v>
       </c>
       <c r="M10" t="n">
-        <v>2.438700693225764</v>
+        <v>2.432229818108214</v>
       </c>
       <c r="N10" t="n">
-        <v>9.140994050501318</v>
+        <v>9.110563456388947</v>
       </c>
       <c r="O10" t="n">
-        <v>3.023407688437224</v>
+        <v>3.018370993829113</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9231023002749</v>
+        <v>367.9307873787741</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31264,7 +31382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K590"/>
+  <dimension ref="A1:K592"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64754,7 +64872,7 @@
     <row r="589">
       <c r="A589" s="1" t="inlineStr">
         <is>
-          <t>2026-01-31 22:20:38+00:00</t>
+          <t>2026-02-08 22:20:25+00:00</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -64764,7 +64882,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>-45.36292155829361,170.86266810436413</t>
+          <t>-45.3629189641966,170.8624854834732</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -64774,94 +64892,208 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>-45.36405465553258,170.86279713868802</t>
+          <t>-45.364052130911375,170.86280791992593</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>-45.36464892545015,170.86305214109126</t>
+          <t>-45.36464876462814,170.86305273716138</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>-45.36528848314787,170.863195057404</t>
+          <t>-45.365290146516664,170.86318736949596</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>-45.365882008975376,170.86345162335792</t>
+          <t>-45.36588012740198,170.8634594795596</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>-45.36637419666749,170.86391319605866</t>
+          <t>-45.36636719262284,170.86392600596952</t>
         </is>
       </c>
       <c r="J589" t="inlineStr">
         <is>
-          <t>-45.36665718936792,170.86464334513397</t>
+          <t>-45.36665649342299,170.86464415430896</t>
         </is>
       </c>
       <c r="K589" t="inlineStr">
         <is>
-          <t>L9</t>
+          <t>L8</t>
         </is>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
         <is>
-          <t>2026-02-08 22:20:25+00:00</t>
+          <t>2026-03-05 22:14:07+00:00</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>-45.36228460522993,170.8623923790947</t>
+          <t>-45.36228665307234,170.8623552209645</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>-45.36292394910005,170.8628364320999</t>
+          <t>-45.362918645126086,170.86246302276456</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>-45.36350972485036,170.8625672343027</t>
+          <t>-45.36351460290047,170.86248878197668</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>-45.364052130911375,170.86280791992593</t>
+          <t>-45.36405698158716,170.86278720541185</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>-45.36464876462814,170.86305273716138</t>
+          <t>-45.36464744588756,170.86305762493626</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>-45.365290146516664,170.86318736949596</t>
+          <t>-45.36529540064635,170.86316308546614</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>-45.36588012740198,170.8634594795596</t>
+          <t>-45.365883919495495,170.86344364629107</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>-45.36636719262284,170.86392600596952</t>
+          <t>-45.36637805716389,170.86390613547653</t>
         </is>
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>-45.36665649342299,170.86464415430896</t>
+          <t>-45.36665885963574,170.86464140311384</t>
         </is>
       </c>
       <c r="K590" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:36+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-45.362287389451055,170.86234185930758</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-45.36291818826743,170.86243086311424</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-45.36351739372163,170.8624438975775</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-45.36406171879314,170.86276697544454</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-45.364653524958236,170.86303509348437</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-45.365296219128396,170.86315930252644</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-45.365888290531814,170.86342539572712</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>-45.366390410749325,170.86388354160727</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>-45.36667514474513,170.86462246841182</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-45.36228877804664,170.86231666303942</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-45.36291823540407,170.86243418117337</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-45.36351797085808,170.8624346155341</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-45.36406495257238,170.86275316576442</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-45.36465674139592,170.86302317207935</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>-45.36529838414479,170.86314929604023</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>-45.36589017210282,170.86341753952328</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>-45.36640425337745,170.86385822435824</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>-45.36667952919708,170.86461737060557</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K592"/>
+  <dimension ref="A1:K596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23516,6 +23516,162 @@
         <v>364.25</v>
       </c>
       <c r="K592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="C593" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="D593" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="E593" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="F593" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="G593" t="n">
+        <v>341.26</v>
+      </c>
+      <c r="H593" t="n">
+        <v>347.25</v>
+      </c>
+      <c r="I593" t="n">
+        <v>352.48</v>
+      </c>
+      <c r="J593" t="n">
+        <v>364.37</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>349.49</v>
+      </c>
+      <c r="C594" t="n">
+        <v>352.37</v>
+      </c>
+      <c r="D594" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="E594" t="n">
+        <v>363.49</v>
+      </c>
+      <c r="F594" t="n">
+        <v>360.37</v>
+      </c>
+      <c r="G594" t="n">
+        <v>341.26</v>
+      </c>
+      <c r="H594" t="n">
+        <v>349.44</v>
+      </c>
+      <c r="I594" t="n">
+        <v>352.48</v>
+      </c>
+      <c r="J594" t="n">
+        <v>362.7</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>346.97</v>
+      </c>
+      <c r="C595" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="D595" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="E595" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="F595" t="n">
+        <v>357.77</v>
+      </c>
+      <c r="G595" t="n">
+        <v>338.28</v>
+      </c>
+      <c r="H595" t="n">
+        <v>346.88</v>
+      </c>
+      <c r="I595" t="n">
+        <v>350.33</v>
+      </c>
+      <c r="J595" t="n">
+        <v>360.41</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>347.14</v>
+      </c>
+      <c r="C596" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="D596" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="E596" t="n">
+        <v>359.92</v>
+      </c>
+      <c r="F596" t="n">
+        <v>356.72</v>
+      </c>
+      <c r="G596" t="n">
+        <v>337.76</v>
+      </c>
+      <c r="H596" t="n">
+        <v>346.28</v>
+      </c>
+      <c r="I596" t="n">
+        <v>349.62</v>
+      </c>
+      <c r="J596" t="n">
+        <v>360.09</v>
+      </c>
+      <c r="K596" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23532,7 +23688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B698"/>
+  <dimension ref="A1:B703"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30515,6 +30671,56 @@
       </c>
       <c r="B698" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -30683,28 +30889,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1603169696694472</v>
+        <v>-0.1706360512159743</v>
       </c>
       <c r="J2" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K2" t="n">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06687711588501732</v>
+        <v>0.07479186094531465</v>
       </c>
       <c r="M2" t="n">
-        <v>3.199316860016856</v>
+        <v>3.225426497439579</v>
       </c>
       <c r="N2" t="n">
-        <v>16.14260443829786</v>
+        <v>16.35435819969182</v>
       </c>
       <c r="O2" t="n">
-        <v>4.017786012009333</v>
+        <v>4.044052200416288</v>
       </c>
       <c r="P2" t="n">
-        <v>359.3941127999129</v>
+        <v>359.5180747602795</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30765,28 +30971,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.761947386619969</v>
+        <v>-6.708792971632726</v>
       </c>
       <c r="J3" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K3" t="n">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4923112056767457</v>
+        <v>0.4912976801202443</v>
       </c>
       <c r="M3" t="n">
-        <v>34.87515615854517</v>
+        <v>34.81154822890338</v>
       </c>
       <c r="N3" t="n">
-        <v>2071.565979186759</v>
+        <v>2065.49353445262</v>
       </c>
       <c r="O3" t="n">
-        <v>45.51445901234858</v>
+        <v>45.44770109095311</v>
       </c>
       <c r="P3" t="n">
-        <v>496.7527925208965</v>
+        <v>496.1061766408502</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -30847,28 +31053,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0406559076666504</v>
+        <v>0.02853251952947525</v>
       </c>
       <c r="J4" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K4" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005162296546497913</v>
+        <v>0.002511564733204907</v>
       </c>
       <c r="M4" t="n">
-        <v>2.867294818466535</v>
+        <v>2.897288243411567</v>
       </c>
       <c r="N4" t="n">
-        <v>14.28232167044102</v>
+        <v>14.62406475816966</v>
       </c>
       <c r="O4" t="n">
-        <v>3.7791959026281</v>
+        <v>3.824142355897549</v>
       </c>
       <c r="P4" t="n">
-        <v>364.8608998525371</v>
+        <v>365.0066340272268</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -30929,28 +31135,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04158908521962487</v>
+        <v>-0.0489817164271644</v>
       </c>
       <c r="J5" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K5" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0077475595654245</v>
+        <v>0.010690313099041</v>
       </c>
       <c r="M5" t="n">
-        <v>2.476995145919434</v>
+        <v>2.496561806317641</v>
       </c>
       <c r="N5" t="n">
-        <v>9.932491166558931</v>
+        <v>10.04232327882014</v>
       </c>
       <c r="O5" t="n">
-        <v>3.151585500436079</v>
+        <v>3.168962492491847</v>
       </c>
       <c r="P5" t="n">
-        <v>367.8807641339326</v>
+        <v>367.9696426702993</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31007,28 +31213,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09000085940175238</v>
+        <v>-0.09453651186171892</v>
       </c>
       <c r="J6" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K6" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02212972118650491</v>
+        <v>0.02461489598594147</v>
       </c>
       <c r="M6" t="n">
-        <v>3.133211069598623</v>
+        <v>3.130101024453504</v>
       </c>
       <c r="N6" t="n">
-        <v>16.04873541054891</v>
+        <v>16.0177541625058</v>
       </c>
       <c r="O6" t="n">
-        <v>4.006087294424437</v>
+        <v>4.002218655009468</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2130700014486</v>
+        <v>364.2676085853115</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31085,28 +31291,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1413921268547371</v>
+        <v>-0.1508261198113272</v>
       </c>
       <c r="J7" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K7" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09079257354535886</v>
+        <v>0.1006656483420341</v>
       </c>
       <c r="M7" t="n">
-        <v>2.411424485314017</v>
+        <v>2.443942012836727</v>
       </c>
       <c r="N7" t="n">
-        <v>8.97646418483335</v>
+        <v>9.19215558023722</v>
       </c>
       <c r="O7" t="n">
-        <v>2.996074796268169</v>
+        <v>3.031856787553993</v>
       </c>
       <c r="P7" t="n">
-        <v>349.6704235190339</v>
+        <v>349.783837784818</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31167,28 +31373,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2266252903754431</v>
+        <v>-0.2289550632887795</v>
       </c>
       <c r="J8" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K8" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1707937008400225</v>
+        <v>0.1756097206892209</v>
       </c>
       <c r="M8" t="n">
-        <v>2.355951298134685</v>
+        <v>2.352854400067701</v>
       </c>
       <c r="N8" t="n">
-        <v>11.18020303573767</v>
+        <v>11.13035911198779</v>
       </c>
       <c r="O8" t="n">
-        <v>3.343681060708043</v>
+        <v>3.336219284158011</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0414820830692</v>
+        <v>355.0694898901346</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31245,28 +31451,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1439169774793705</v>
+        <v>-0.1537116407220695</v>
       </c>
       <c r="J9" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K9" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06521124249016474</v>
+        <v>0.07329142666636479</v>
       </c>
       <c r="M9" t="n">
-        <v>2.607570477867351</v>
+        <v>2.638388382262499</v>
       </c>
       <c r="N9" t="n">
-        <v>13.31242776953138</v>
+        <v>13.5122565962228</v>
       </c>
       <c r="O9" t="n">
-        <v>3.648619981517859</v>
+        <v>3.675902147258928</v>
       </c>
       <c r="P9" t="n">
-        <v>361.5637612369828</v>
+        <v>361.6815052227961</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31323,28 +31529,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09956395449253129</v>
+        <v>-0.1046711704345391</v>
       </c>
       <c r="J10" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K10" t="n">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04651725469207257</v>
+        <v>0.05139945513723432</v>
       </c>
       <c r="M10" t="n">
-        <v>2.432229818108214</v>
+        <v>2.436716633370594</v>
       </c>
       <c r="N10" t="n">
-        <v>9.110563456388947</v>
+        <v>9.145414155529071</v>
       </c>
       <c r="O10" t="n">
-        <v>3.018370993829113</v>
+        <v>3.024138580741476</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9307873787741</v>
+        <v>367.9922025262138</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31382,7 +31588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K592"/>
+  <dimension ref="A1:K596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65097,6 +65303,234 @@
         </is>
       </c>
     </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:13:58+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-45.362289381172296,170.86230571920547</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-45.362918132065936,170.86242690696685</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-45.36351855589972,170.86242520633934</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-45.36406739208892,170.8627427479345</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-45.36465638758783,170.86302448343397</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>-45.365299255431644,170.8631452690395</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>-45.365889101054776,170.86342201151632</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>-45.36640248858057,170.863861452056</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>-45.36667869406339,170.86461834161636</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-45.362289381172296,170.86230571920547</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-45.362918132065936,170.86242690696685</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-45.36351855589972,170.86242520633934</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-45.36406739208892,170.8627427479345</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-45.36465638758783,170.86302448343397</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>-45.365299255431644,170.8631452690395</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>-45.365882761604574,170.8634484808771</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>-45.36640248858057,170.863861452056</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>-45.366690316339714,170.86460482838044</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-45.3622911484646,170.86227365122573</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-45.36291788006401,170.86240916811252</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-45.36352039007929,170.86239570724103</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-45.36407573182421,170.8627071334862</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-45.36466475032021,170.86299348777516</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>-45.36530712340926,170.86310890399704</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>-45.36589017210282,170.86341753952328</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>-45.3664143458078,170.86383976595778</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>-45.36670625347031,170.86458629824554</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-45.36229102924278,170.86227581454187</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-45.362917742277624,170.86239946917073</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-45.363520769563756,170.8623896039791</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-45.36407751890887,170.8626995018174</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>-45.36466812757507,170.86298097029507</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>-45.36530849634374,170.86310255841818</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>-45.36589190893711,170.86341028764232</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>-45.366418261449326,170.86383260450012</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>-45.366708480492676,170.86458370888087</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K596"/>
+  <dimension ref="A1:K602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23672,6 +23672,240 @@
         <v>360.09</v>
       </c>
       <c r="K596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>347.98</v>
+      </c>
+      <c r="C597" t="n">
+        <v>350.03</v>
+      </c>
+      <c r="D597" t="n">
+        <v>356.92</v>
+      </c>
+      <c r="E597" t="n">
+        <v>360.39</v>
+      </c>
+      <c r="F597" t="n">
+        <v>357.24</v>
+      </c>
+      <c r="G597" t="n">
+        <v>338.55</v>
+      </c>
+      <c r="H597" t="n">
+        <v>346.33</v>
+      </c>
+      <c r="I597" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="J597" t="n">
+        <v>360.51</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="C598" t="n">
+        <v>350.71</v>
+      </c>
+      <c r="D598" t="n">
+        <v>357.13</v>
+      </c>
+      <c r="E598" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="F598" t="n">
+        <v>357.25</v>
+      </c>
+      <c r="G598" t="n">
+        <v>338.64</v>
+      </c>
+      <c r="H598" t="n">
+        <v>346.44</v>
+      </c>
+      <c r="I598" t="n">
+        <v>350.3</v>
+      </c>
+      <c r="J598" t="n">
+        <v>360.18</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="C599" t="n">
+        <v>350.98</v>
+      </c>
+      <c r="D599" t="n">
+        <v>357.62</v>
+      </c>
+      <c r="E599" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="F599" t="n">
+        <v>357.03</v>
+      </c>
+      <c r="G599" t="n">
+        <v>338.61</v>
+      </c>
+      <c r="H599" t="n">
+        <v>346.63</v>
+      </c>
+      <c r="I599" t="n">
+        <v>350.83</v>
+      </c>
+      <c r="J599" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="C600" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="D600" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="E600" t="n">
+        <v>362.4</v>
+      </c>
+      <c r="F600" t="n">
+        <v>357.94</v>
+      </c>
+      <c r="G600" t="n">
+        <v>339.63</v>
+      </c>
+      <c r="H600" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="I600" t="n">
+        <v>352.05</v>
+      </c>
+      <c r="J600" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>350.27</v>
+      </c>
+      <c r="C601" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="D601" t="n">
+        <v>360.36</v>
+      </c>
+      <c r="E601" t="n">
+        <v>363.62</v>
+      </c>
+      <c r="F601" t="n">
+        <v>359.85</v>
+      </c>
+      <c r="G601" t="n">
+        <v>340.62</v>
+      </c>
+      <c r="H601" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="I601" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="J601" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>350.27</v>
+      </c>
+      <c r="C602" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="D602" t="n">
+        <v>359.76</v>
+      </c>
+      <c r="E602" t="n">
+        <v>362.88</v>
+      </c>
+      <c r="F602" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="G602" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="H602" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="I602" t="n">
+        <v>352.62</v>
+      </c>
+      <c r="J602" t="n">
+        <v>361.03</v>
+      </c>
+      <c r="K602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23688,7 +23922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B703"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30721,6 +30955,76 @@
       </c>
       <c r="B703" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -30889,28 +31193,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1706360512159743</v>
+        <v>-0.1842559107049379</v>
       </c>
       <c r="J2" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07479186094531465</v>
+        <v>0.08606884896087785</v>
       </c>
       <c r="M2" t="n">
-        <v>3.225426497439579</v>
+        <v>3.256808657701281</v>
       </c>
       <c r="N2" t="n">
-        <v>16.35435819969182</v>
+        <v>16.57702050665725</v>
       </c>
       <c r="O2" t="n">
-        <v>4.044052200416288</v>
+        <v>4.071488733455767</v>
       </c>
       <c r="P2" t="n">
-        <v>359.5180747602795</v>
+        <v>359.6821863583062</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30971,28 +31275,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.708792971632726</v>
+        <v>-6.630821022794785</v>
       </c>
       <c r="J3" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4912976801202443</v>
+        <v>0.4897633545078137</v>
       </c>
       <c r="M3" t="n">
-        <v>34.81154822890338</v>
+        <v>34.71573280331418</v>
       </c>
       <c r="N3" t="n">
-        <v>2065.49353445262</v>
+        <v>2056.459685302412</v>
       </c>
       <c r="O3" t="n">
-        <v>45.44770109095311</v>
+        <v>45.34820487408969</v>
       </c>
       <c r="P3" t="n">
-        <v>496.1061766408502</v>
+        <v>495.154480637944</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31053,28 +31357,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02853251952947525</v>
+        <v>0.01252254020017653</v>
       </c>
       <c r="J4" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002511564733204907</v>
+        <v>0.0004784801776559489</v>
       </c>
       <c r="M4" t="n">
-        <v>2.897288243411567</v>
+        <v>2.936151167338013</v>
       </c>
       <c r="N4" t="n">
-        <v>14.62406475816966</v>
+        <v>15.00614549355645</v>
       </c>
       <c r="O4" t="n">
-        <v>3.824142355897549</v>
+        <v>3.87377664476883</v>
       </c>
       <c r="P4" t="n">
-        <v>365.0066340272268</v>
+        <v>365.1996723281907</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31135,28 +31439,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0489817164271644</v>
+        <v>-0.05966694357656062</v>
       </c>
       <c r="J5" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K5" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.010690313099041</v>
+        <v>0.01576113662616618</v>
       </c>
       <c r="M5" t="n">
-        <v>2.496561806317641</v>
+        <v>2.523937668209439</v>
       </c>
       <c r="N5" t="n">
-        <v>10.04232327882014</v>
+        <v>10.1844280595145</v>
       </c>
       <c r="O5" t="n">
-        <v>3.168962492491847</v>
+        <v>3.191305071520818</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9696426702993</v>
+        <v>368.0984705258426</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31213,28 +31517,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09453651186171892</v>
+        <v>-0.102577944684255</v>
       </c>
       <c r="J6" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K6" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02461489598594147</v>
+        <v>0.02924816757742765</v>
       </c>
       <c r="M6" t="n">
-        <v>3.130101024453504</v>
+        <v>3.130525179211145</v>
       </c>
       <c r="N6" t="n">
-        <v>16.0177541625058</v>
+        <v>15.99829232872903</v>
       </c>
       <c r="O6" t="n">
-        <v>4.002218655009468</v>
+        <v>3.999786535395236</v>
       </c>
       <c r="P6" t="n">
-        <v>364.2676085853115</v>
+        <v>364.364561279215</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31291,28 +31595,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1508261198113272</v>
+        <v>-0.1647801874091933</v>
       </c>
       <c r="J7" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K7" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1006656483420341</v>
+        <v>0.1158184554208405</v>
       </c>
       <c r="M7" t="n">
-        <v>2.443942012836727</v>
+        <v>2.492780184755973</v>
       </c>
       <c r="N7" t="n">
-        <v>9.19215558023722</v>
+        <v>9.495760387895274</v>
       </c>
       <c r="O7" t="n">
-        <v>3.031856787553993</v>
+        <v>3.081519168834631</v>
       </c>
       <c r="P7" t="n">
-        <v>349.783837784818</v>
+        <v>349.9520951992251</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31373,28 +31677,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2289550632887795</v>
+        <v>-0.2330938799507017</v>
       </c>
       <c r="J8" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K8" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1756097206892209</v>
+        <v>0.1837328085954163</v>
       </c>
       <c r="M8" t="n">
-        <v>2.352854400067701</v>
+        <v>2.349133084283632</v>
       </c>
       <c r="N8" t="n">
-        <v>11.13035911198779</v>
+        <v>11.05766566336704</v>
       </c>
       <c r="O8" t="n">
-        <v>3.336219284158011</v>
+        <v>3.325306852512568</v>
       </c>
       <c r="P8" t="n">
-        <v>355.0694898901346</v>
+        <v>355.1193849442501</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31451,28 +31755,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1537116407220695</v>
+        <v>-0.1671165543464541</v>
       </c>
       <c r="J9" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K9" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07329142666636479</v>
+        <v>0.08513457059372187</v>
       </c>
       <c r="M9" t="n">
-        <v>2.638388382262499</v>
+        <v>2.681329039748351</v>
       </c>
       <c r="N9" t="n">
-        <v>13.5122565962228</v>
+        <v>13.74821445261353</v>
       </c>
       <c r="O9" t="n">
-        <v>3.675902147258928</v>
+        <v>3.707858472570593</v>
       </c>
       <c r="P9" t="n">
-        <v>361.6815052227961</v>
+        <v>361.8431320568892</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31529,28 +31833,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1046711704345391</v>
+        <v>-0.1143268757900957</v>
       </c>
       <c r="J10" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="K10" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05139945513723432</v>
+        <v>0.06084014029818585</v>
       </c>
       <c r="M10" t="n">
-        <v>2.436716633370594</v>
+        <v>2.451930925347115</v>
       </c>
       <c r="N10" t="n">
-        <v>9.145414155529071</v>
+        <v>9.242768429482647</v>
       </c>
       <c r="O10" t="n">
-        <v>3.024138580741476</v>
+        <v>3.040192169827863</v>
       </c>
       <c r="P10" t="n">
-        <v>367.9922025262138</v>
+        <v>368.1086347667143</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31588,7 +31892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K596"/>
+  <dimension ref="A1:K602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65531,6 +65835,348 @@
         </is>
       </c>
     </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-45.36229044014615,170.8622865038686</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-45.362917707830896,170.86239704443528</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-45.36352033473778,170.86239659730003</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-45.36407618568703,170.86270519528466</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-45.364666455029976,170.86298716942824</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>-45.36530641053928,170.86311219881676</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-45.365891764200924,170.86341089196574</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-45.366415614255104,170.86383744604908</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-45.36670555752581,170.86458710742195</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:13:53+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-45.36229109937326,170.86227454200298</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-45.36291783111368,170.86240572243582</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-45.363520168713194,170.86239926747712</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-45.36407573182421,170.8627071334862</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-45.364666422865646,170.86298728864236</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-45.36530617291594,170.86311329708994</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-45.365891445781344,170.8634122214773</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-45.366414511257446,170.863839463361</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>-45.36670785414264,170.8645844371397</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-45.3622905032637,170.86228535858362</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-45.36291788006401,170.86240916811252</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-45.36351978132226,170.86240549789022</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-45.36407437023554,170.8627129480907</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-45.36466713048093,170.8629846659322</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>-45.365306252123716,170.86311293099888</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-45.36589089578383,170.86341451790625</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-45.366411588313476,170.86384480923724</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>-45.3667073669815,170.86458500356323</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-45.362289591564696,170.8623019015889</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-45.362918121188216,170.8624261412609</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-45.36351853218183,170.86242558779315</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-45.364070484032915,170.86272954393954</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-45.364664203526424,170.86299551441465</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>-45.36530355905843,170.86312537809468</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-45.36588904316027,170.86342225324563</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-45.36640486002635,170.86385711483706</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>-45.36670096429196,170.8645924479858</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-45.3622888341514,170.86231564500835</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-45.36291825534645,170.8624355849676</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-45.36351761508912,170.86244033734167</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-45.364067023324864,170.8627443227228</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-45.36465806013499,170.8630182843029</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-45.36530094519963,170.8631374590983</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-45.36588724843071,170.86342974685522</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-45.366399345035894,170.86386720139217</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>-45.36669692781349,170.86459714120787</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:42+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-45.3622888341514,170.86231564500835</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-45.36291825534645,170.8624355849676</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-45.363518089447666,170.8624327082649</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-45.364069122443084,170.862735358543</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-45.36466002216104,170.8630110122449</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-45.3653012884337,170.86313587270396</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-45.36588724843071,170.86342974685522</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-45.366401716481896,170.8638628641737</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>-45.36670193861432,170.864591315139</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0485/nzd0485.xlsx
+++ b/data/nzd0485/nzd0485.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K602"/>
+  <dimension ref="A1:K604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23906,6 +23906,84 @@
         <v>361.03</v>
       </c>
       <c r="K602" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>351.46</v>
+      </c>
+      <c r="C603" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="D603" t="n">
+        <v>359.73</v>
+      </c>
+      <c r="E603" t="n">
+        <v>363.66</v>
+      </c>
+      <c r="F603" t="n">
+        <v>359.9</v>
+      </c>
+      <c r="G603" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="H603" t="n">
+        <v>348.53</v>
+      </c>
+      <c r="I603" t="n">
+        <v>353.07</v>
+      </c>
+      <c r="J603" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>352.1</v>
+      </c>
+      <c r="C604" t="n">
+        <v>351.96</v>
+      </c>
+      <c r="D604" t="n">
+        <v>360.59</v>
+      </c>
+      <c r="E604" t="n">
+        <v>364.52</v>
+      </c>
+      <c r="F604" t="n">
+        <v>360.45</v>
+      </c>
+      <c r="G604" t="n">
+        <v>340.47</v>
+      </c>
+      <c r="H604" t="n">
+        <v>348.7</v>
+      </c>
+      <c r="I604" t="n">
+        <v>353.64</v>
+      </c>
+      <c r="J604" t="n">
+        <v>361.62</v>
+      </c>
+      <c r="K604" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23922,7 +24000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31025,6 +31103,26 @@
       </c>
       <c r="B710" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -31193,28 +31291,28 @@
         <v>0.0741</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1842559107049379</v>
+        <v>-0.1864274556990391</v>
       </c>
       <c r="J2" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K2" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08606884896087785</v>
+        <v>0.08839090320865406</v>
       </c>
       <c r="M2" t="n">
-        <v>3.256808657701281</v>
+        <v>3.256229078951844</v>
       </c>
       <c r="N2" t="n">
-        <v>16.57702050665725</v>
+        <v>16.55102744412737</v>
       </c>
       <c r="O2" t="n">
-        <v>4.071488733455767</v>
+        <v>4.06829539784507</v>
       </c>
       <c r="P2" t="n">
-        <v>359.6821863583062</v>
+        <v>359.7084487276803</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31275,28 +31373,28 @@
         <v>0.1189</v>
       </c>
       <c r="I3" t="n">
-        <v>-6.630821022794785</v>
+        <v>-6.604901107699395</v>
       </c>
       <c r="J3" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K3" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4897633545078137</v>
+        <v>0.4892166744604319</v>
       </c>
       <c r="M3" t="n">
-        <v>34.71573280331418</v>
+        <v>34.68542076466553</v>
       </c>
       <c r="N3" t="n">
-        <v>2056.459685302412</v>
+        <v>2053.560371815158</v>
       </c>
       <c r="O3" t="n">
-        <v>45.34820487408969</v>
+        <v>45.31622636335861</v>
       </c>
       <c r="P3" t="n">
-        <v>495.154480637944</v>
+        <v>494.8370233851398</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -31357,28 +31455,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01252254020017653</v>
+        <v>0.008581409393957152</v>
       </c>
       <c r="J4" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K4" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004784801776559489</v>
+        <v>0.0002250153760940954</v>
       </c>
       <c r="M4" t="n">
-        <v>2.936151167338013</v>
+        <v>2.943375245844183</v>
       </c>
       <c r="N4" t="n">
-        <v>15.00614549355645</v>
+        <v>15.05169430810345</v>
       </c>
       <c r="O4" t="n">
-        <v>3.87377664476883</v>
+        <v>3.879651312695955</v>
       </c>
       <c r="P4" t="n">
-        <v>365.1996723281907</v>
+        <v>365.2473663574006</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -31439,28 +31537,28 @@
         <v>0.0955</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05966694357656062</v>
+        <v>-0.06143440755290709</v>
       </c>
       <c r="J5" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K5" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01576113662616618</v>
+        <v>0.01678479251861353</v>
       </c>
       <c r="M5" t="n">
-        <v>2.523937668209439</v>
+        <v>2.524304596465187</v>
       </c>
       <c r="N5" t="n">
-        <v>10.1844280595145</v>
+        <v>10.17030636516232</v>
       </c>
       <c r="O5" t="n">
-        <v>3.191305071520818</v>
+        <v>3.189091777475575</v>
       </c>
       <c r="P5" t="n">
-        <v>368.0984705258426</v>
+        <v>368.1198588486968</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31517,28 +31615,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.102577944684255</v>
+        <v>-0.1036351329295182</v>
       </c>
       <c r="J6" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K6" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02924816757742765</v>
+        <v>0.03004151285767709</v>
       </c>
       <c r="M6" t="n">
-        <v>3.130525179211145</v>
+        <v>3.124326341076079</v>
       </c>
       <c r="N6" t="n">
-        <v>15.99829232872903</v>
+        <v>15.95230491390648</v>
       </c>
       <c r="O6" t="n">
-        <v>3.999786535395236</v>
+        <v>3.994033664593537</v>
       </c>
       <c r="P6" t="n">
-        <v>364.364561279215</v>
+        <v>364.3773543743302</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31595,28 +31693,28 @@
         <v>0.1017</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1647801874091933</v>
+        <v>-0.1686438717250598</v>
       </c>
       <c r="J7" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K7" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1158184554208405</v>
+        <v>0.1204313448361967</v>
       </c>
       <c r="M7" t="n">
-        <v>2.492780184755973</v>
+        <v>2.504912718504243</v>
       </c>
       <c r="N7" t="n">
-        <v>9.495760387895274</v>
+        <v>9.555411908419869</v>
       </c>
       <c r="O7" t="n">
-        <v>3.081519168834631</v>
+        <v>3.091182930274407</v>
       </c>
       <c r="P7" t="n">
-        <v>349.9520951992251</v>
+        <v>349.9988527913047</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31677,28 +31775,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2330938799507017</v>
+        <v>-0.2332823606019113</v>
       </c>
       <c r="J8" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K8" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1837328085954163</v>
+        <v>0.185103339534706</v>
       </c>
       <c r="M8" t="n">
-        <v>2.349133084283632</v>
+        <v>2.342238940014466</v>
       </c>
       <c r="N8" t="n">
-        <v>11.05766566336704</v>
+        <v>11.0212324727994</v>
       </c>
       <c r="O8" t="n">
-        <v>3.325306852512568</v>
+        <v>3.319824162933844</v>
       </c>
       <c r="P8" t="n">
-        <v>355.1193849442501</v>
+        <v>355.1216656234827</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31755,28 +31853,28 @@
         <v>0.0891</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1671165543464541</v>
+        <v>-0.1700566286171392</v>
       </c>
       <c r="J9" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K9" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08513457059372187</v>
+        <v>0.08818459129385725</v>
       </c>
       <c r="M9" t="n">
-        <v>2.681329039748351</v>
+        <v>2.687813294426141</v>
       </c>
       <c r="N9" t="n">
-        <v>13.74821445261353</v>
+        <v>13.75559647084552</v>
       </c>
       <c r="O9" t="n">
-        <v>3.707858472570593</v>
+        <v>3.708853794751893</v>
       </c>
       <c r="P9" t="n">
-        <v>361.8431320568892</v>
+        <v>361.8787118043097</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31833,28 +31931,28 @@
         <v>0.0886</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1143268757900957</v>
+        <v>-0.1170521165628195</v>
       </c>
       <c r="J10" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="K10" t="n">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06084014029818585</v>
+        <v>0.06374262618722881</v>
       </c>
       <c r="M10" t="n">
-        <v>2.451930925347115</v>
+        <v>2.45501009291614</v>
       </c>
       <c r="N10" t="n">
-        <v>9.242768429482647</v>
+        <v>9.257674728094026</v>
       </c>
       <c r="O10" t="n">
-        <v>3.040192169827863</v>
+        <v>3.042642721072263</v>
       </c>
       <c r="P10" t="n">
-        <v>368.1086347667143</v>
+        <v>368.1416145968582</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31892,7 +31990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K602"/>
+  <dimension ref="A1:K604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66177,6 +66275,120 @@
         </is>
       </c>
     </row>
+    <row r="603">
+      <c r="A603" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>-45.362287999592226,170.8623307882202</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>-45.36291812300116,170.86242626887855</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>-45.36351811316556,170.86243232681107</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>-45.36406690985898,170.86274480727303</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>-45.364657899313166,170.8630188803732</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>-45.36530239734357,170.86313074742975</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>-45.36588539580611,170.86343748219363</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>-45.36639923473606,170.86386740312327</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>-45.36670186901986,170.86459139605662</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>-45.36228755075285,170.8623389324684</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>-45.36291805773471,170.8624216746429</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>-45.363517433251545,170.86244326182108</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>-45.364064470342235,170.86275522510275</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>-45.36465613027285,170.8630254371464</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>-45.36530134123893,170.86313562864328</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>-45.3658849037026,170.86343953689283</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>-45.366396091191056,170.86387315245875</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>-45.36669783254145,170.86459608927885</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
